--- a/packages/office-reader/src/spreadsheet/fixtures/date1904.xlsx
+++ b/packages/office-reader/src/spreadsheet/fixtures/date1904.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cellXfs count="2">
     <xf numFmtId="0"/>
     <xf numFmtId="14"/>
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<x:workbook xmlns:x="https://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="https://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <x:workbookPr date1904="1"/>
   <x:sheets>
     <x:sheet name="d" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1">
